--- a/public/template/template_tracer.xlsx
+++ b/public/template/template_tracer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\tracer-system\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AB5C786-CB21-4BE9-AA62-A5E32819C63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA78929C-D27F-42C2-83DC-3C42DD0618A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
   <si>
     <t>Nama Lengkap</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Kota</t>
   </si>
   <si>
-    <t>Contoh</t>
-  </si>
-  <si>
     <t>Sebutkan sumber dana dalam pembiayaan kuliah di Universitas Harkat Negeri?</t>
   </si>
   <si>
@@ -283,21 +280,6 @@
     <t>Jika menurut Anda pekerjaan Anda saat ini tidak sesuai dengan pendidikan Anda, mengapa Anda mengambilnya? - Pada awal meniti karir ini, saya harus menerima pekerjaan yang tidak berhubungan dengan pendidikan saya</t>
   </si>
   <si>
-    <t>Adhie Febriansah Cahyono Putra</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 33282702869810</t>
-  </si>
-  <si>
-    <t>D3 Teknik Mesin</t>
-  </si>
-  <si>
-    <t>085974854769</t>
-  </si>
-  <si>
     <t>Harjasari</t>
   </si>
   <si>
@@ -305,17 +287,177 @@
   </si>
   <si>
     <t>Tegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faris Iman Rozandi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3328175190176182</t>
+  </si>
+  <si>
+    <t>D4 Teknik Informatika</t>
+  </si>
+  <si>
+    <t>083837361874</t>
+  </si>
+  <si>
+    <t>Jembayat</t>
+  </si>
+  <si>
+    <t>Margasari</t>
+  </si>
+  <si>
+    <t>Rizqi Surowati</t>
+  </si>
+  <si>
+    <t>081990721212</t>
+  </si>
+  <si>
+    <t>Pesarean</t>
+  </si>
+  <si>
+    <t>Adiwerna</t>
+  </si>
+  <si>
+    <t>Tidak diizinkan suami/orang tua</t>
+  </si>
+  <si>
+    <t>Fatimatuzzahro</t>
+  </si>
+  <si>
+    <t>087846563905</t>
+  </si>
+  <si>
+    <t>Cabawan</t>
+  </si>
+  <si>
+    <t>Margadana</t>
+  </si>
+  <si>
+    <t>Universitas Brawijaya</t>
+  </si>
+  <si>
+    <t>Teknik Elektro</t>
+  </si>
+  <si>
+    <t>20 Desember 2025</t>
+  </si>
+  <si>
+    <t>Jl. Kenangan</t>
+  </si>
+  <si>
+    <t>Insan Maulana</t>
+  </si>
+  <si>
+    <t>0895377525593</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wahyu Indrawan</t>
+  </si>
+  <si>
+    <t>085326699718</t>
+  </si>
+  <si>
+    <t>Debong Kidul</t>
+  </si>
+  <si>
+    <t>Tegal Selatan</t>
+  </si>
+  <si>
+    <t>Kota Tegal</t>
+  </si>
+  <si>
+    <t>5 - 10 juta</t>
+  </si>
+  <si>
+    <t>Jl Tirus No. 45</t>
+  </si>
+  <si>
+    <t>Toko Sembako Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibu Anggraini </t>
+  </si>
+  <si>
+    <t>082132045093</t>
+  </si>
+  <si>
+    <t>ibuanggraini29@gmail.com</t>
+  </si>
+  <si>
+    <t>Luthfil Khakim</t>
+  </si>
+  <si>
+    <t>081999625470</t>
+  </si>
+  <si>
+    <t>2 - 5 juta</t>
+  </si>
+  <si>
+    <t>Jl Karasidenan</t>
+  </si>
+  <si>
+    <t>Kantor Pajak Yogyakarta</t>
+  </si>
+  <si>
+    <t>Bapak Suwadino</t>
+  </si>
+  <si>
+    <t>085326665058</t>
+  </si>
+  <si>
+    <t>silky.afina.saly@gmail.com</t>
+  </si>
+  <si>
+    <t>Mukhamad Iktafal Ma'arif</t>
+  </si>
+  <si>
+    <t>083861669537</t>
+  </si>
+  <si>
+    <t>Di atas 10 juta</t>
+  </si>
+  <si>
+    <t>Jl. Lebak Bulus No. 50</t>
+  </si>
+  <si>
+    <t>Bidan Sadyta</t>
+  </si>
+  <si>
+    <t>Imam Brilliant Septa Ikhsandria</t>
+  </si>
+  <si>
+    <t>082328597334</t>
+  </si>
+  <si>
+    <t>Grogol</t>
+  </si>
+  <si>
+    <t>Dukuhturi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -338,13 +480,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -644,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CI2"/>
+  <dimension ref="A1:CH9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -657,84 +852,83 @@
     <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="88.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="94.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="126.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="104.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="123.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="100.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="104.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="102.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="109.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="141.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="120.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="139.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="115.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="120.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="117.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="147.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="169.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="141.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="145" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="151" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="53" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="107.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="143.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="62.42578125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="56.5703125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="83.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="53" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="146.140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="69.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="93.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="20" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="56" max="57" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="88.42578125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="109.5703125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="77.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="92" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="73" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="74.28515625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="97.85546875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="135.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="100.140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="97.85546875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="117.85546875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="86" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="115.5703125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="159.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="84.85546875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="73" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="228.85546875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="187.5703125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="194.5703125" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="237.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="250" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="207.5703125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="187.5703125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="172.140625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="251.28515625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="201.7109375" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="210" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="250" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="88.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="94.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="126.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="104.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="123.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="104.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="102.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="109.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="141.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="120.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="139.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="115.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="120.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="117.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="147.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="169.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="141.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="145" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="151" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="53" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="107.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="143.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="62.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="83.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="53" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="146.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="69.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="93.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="20" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="56" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="88.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="109.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="77.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="92" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="73" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="74.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="97.85546875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="135.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="97.85546875" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="117.85546875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="86" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="115.5703125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="159.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="84.85546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="96.7109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="73" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="228.85546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="187.5703125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="194.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="237.140625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="250" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="207.5703125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="187.5703125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="172.140625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="251.28515625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="201.7109375" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="210" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="250" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -993,127 +1187,1233 @@
       <c r="CH1" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" t="s">
+    </row>
+    <row r="2" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="1">
+        <v>17090093</v>
+      </c>
+      <c r="C2" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="1">
+        <v>4</v>
+      </c>
+      <c r="L2" s="1">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1">
+        <v>4</v>
+      </c>
+      <c r="N2" s="1">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1">
+        <v>5</v>
+      </c>
+      <c r="P2" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>5</v>
+      </c>
+      <c r="R2" s="1">
+        <v>4</v>
+      </c>
+      <c r="S2" s="1">
+        <v>5</v>
+      </c>
+      <c r="T2" s="1">
+        <v>5</v>
+      </c>
+      <c r="U2" s="1">
+        <v>5</v>
+      </c>
+      <c r="V2" s="1">
+        <v>5</v>
+      </c>
+      <c r="W2" s="1">
+        <v>5</v>
+      </c>
+      <c r="X2" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1">
+        <v>5</v>
+      </c>
+      <c r="BT2" s="1">
+        <v>4</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>3</v>
+      </c>
+      <c r="BV2" s="1">
+        <v>4</v>
+      </c>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+    </row>
+    <row r="3" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="1">
+        <v>18090072</v>
+      </c>
+      <c r="C3" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" s="1">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1">
+        <v>4</v>
+      </c>
+      <c r="M3" s="1">
+        <v>4</v>
+      </c>
+      <c r="N3" s="1">
+        <v>4</v>
+      </c>
+      <c r="O3" s="1">
+        <v>4</v>
+      </c>
+      <c r="P3" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>4</v>
+      </c>
+      <c r="R3" s="1">
+        <v>4</v>
+      </c>
+      <c r="S3" s="1">
+        <v>4</v>
+      </c>
+      <c r="T3" s="1">
+        <v>4</v>
+      </c>
+      <c r="U3" s="1">
+        <v>4</v>
+      </c>
+      <c r="V3" s="1">
+        <v>4</v>
+      </c>
+      <c r="W3" s="1">
+        <v>4</v>
+      </c>
+      <c r="X3" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>3</v>
+      </c>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1"/>
+      <c r="BE3" s="1"/>
+      <c r="BF3" s="1"/>
+      <c r="BG3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1"/>
+      <c r="BJ3" s="1"/>
+      <c r="BK3" s="1"/>
+      <c r="BL3" s="1"/>
+      <c r="BM3" s="1"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="1"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="1"/>
+      <c r="BS3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BU3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BV3" s="1">
+        <v>2</v>
+      </c>
+      <c r="BW3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BX3" s="1"/>
+      <c r="BY3" s="1"/>
+      <c r="BZ3" s="1"/>
+      <c r="CA3" s="1"/>
+      <c r="CB3" s="1"/>
+      <c r="CC3" s="1"/>
+      <c r="CD3" s="1"/>
+      <c r="CE3" s="1"/>
+      <c r="CF3" s="1"/>
+      <c r="CG3" s="1"/>
+      <c r="CH3" s="1"/>
+    </row>
+    <row r="4" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="1">
+        <v>19090039</v>
+      </c>
+      <c r="C4" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4">
+        <v>4</v>
+      </c>
+      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="R4">
+        <v>4</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>5</v>
+      </c>
+      <c r="U4">
+        <v>5</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>5</v>
+      </c>
+      <c r="X4">
+        <v>5</v>
+      </c>
+      <c r="Y4">
+        <v>5</v>
+      </c>
+      <c r="Z4">
+        <v>2</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>2</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>2</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>4</v>
+      </c>
+      <c r="AV4">
+        <v>2</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>107</v>
+      </c>
+      <c r="BB4">
+        <v>3</v>
+      </c>
+      <c r="BO4">
+        <v>1</v>
+      </c>
+      <c r="BS4">
+        <v>1</v>
+      </c>
+      <c r="BT4">
+        <v>1</v>
+      </c>
+      <c r="BU4">
+        <v>1</v>
+      </c>
+      <c r="BV4">
+        <v>1</v>
+      </c>
+      <c r="BW4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="1">
+        <v>19090043</v>
+      </c>
+      <c r="C5" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>4</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>4</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>5</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
+        <v>5</v>
+      </c>
+      <c r="X5">
+        <v>5</v>
+      </c>
+      <c r="Y5">
+        <v>5</v>
+      </c>
+      <c r="Z5">
+        <v>2</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>4</v>
+      </c>
+      <c r="AV5">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>107</v>
+      </c>
+      <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BO5">
+        <v>1</v>
+      </c>
+      <c r="BS5">
+        <v>1</v>
+      </c>
+      <c r="BT5">
+        <v>1</v>
+      </c>
+      <c r="BU5">
+        <v>1</v>
+      </c>
+      <c r="BV5">
+        <v>1</v>
+      </c>
+      <c r="BW5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2">
-        <v>19020055</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="6" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1">
+        <v>18090108</v>
+      </c>
+      <c r="C6" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>2</v>
+      </c>
+      <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AA6">
+        <v>2</v>
+      </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>4</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK6">
+        <v>36500</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN6">
+        <v>2</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS6">
+        <v>3</v>
+      </c>
+      <c r="AT6">
+        <v>2</v>
+      </c>
+      <c r="BB6">
+        <v>1</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BS6">
+        <v>2</v>
+      </c>
+      <c r="BT6">
+        <v>1</v>
+      </c>
+      <c r="BU6">
+        <v>1</v>
+      </c>
+      <c r="BV6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="1">
+        <v>18090123</v>
+      </c>
+      <c r="C7" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7">
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <v>5</v>
+      </c>
+      <c r="U7">
+        <v>5</v>
+      </c>
+      <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>5</v>
+      </c>
+      <c r="X7">
+        <v>5</v>
+      </c>
+      <c r="Y7">
+        <v>5</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ7">
+        <v>40000</v>
+      </c>
+      <c r="AK7">
+        <v>46000</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN7">
+        <v>2</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS7">
+        <v>2</v>
+      </c>
+      <c r="AT7">
+        <v>2</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BD7">
+        <v>3</v>
+      </c>
+      <c r="BH7">
+        <v>1</v>
+      </c>
+      <c r="BS7">
+        <v>1</v>
+      </c>
+      <c r="BT7">
+        <v>1</v>
+      </c>
+      <c r="BU7">
+        <v>1</v>
+      </c>
+      <c r="BV7">
+        <v>1</v>
+      </c>
+      <c r="BW7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="1">
+        <v>19090022</v>
+      </c>
+      <c r="C8" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F2">
-        <v>2022</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E8" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-      <c r="O2">
-        <v>5</v>
-      </c>
-      <c r="P2">
-        <v>5</v>
-      </c>
-      <c r="Q2">
-        <v>4</v>
-      </c>
-      <c r="R2">
-        <v>5</v>
-      </c>
-      <c r="S2">
-        <v>4</v>
-      </c>
-      <c r="T2">
-        <v>5</v>
-      </c>
-      <c r="U2">
-        <v>5</v>
-      </c>
-      <c r="V2">
-        <v>5</v>
-      </c>
-      <c r="W2">
-        <v>5</v>
-      </c>
-      <c r="X2">
-        <v>5</v>
-      </c>
-      <c r="Y2">
-        <v>5</v>
-      </c>
-      <c r="Z2">
-        <v>5</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>1</v>
-      </c>
-      <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2">
-        <v>1</v>
-      </c>
-      <c r="AG2">
-        <v>5</v>
-      </c>
-      <c r="BN2">
-        <v>1</v>
-      </c>
-      <c r="BT2">
-        <v>5</v>
-      </c>
-      <c r="BU2">
-        <v>4</v>
-      </c>
-      <c r="BV2">
+      <c r="F8" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>5</v>
+      </c>
+      <c r="Q8">
+        <v>5</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
+        <v>5</v>
+      </c>
+      <c r="U8">
+        <v>5</v>
+      </c>
+      <c r="V8">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>5</v>
+      </c>
+      <c r="X8">
+        <v>5</v>
+      </c>
+      <c r="Y8">
+        <v>5</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
         <v>3</v>
       </c>
-      <c r="BW2">
-        <v>4</v>
-      </c>
-      <c r="BY2">
+      <c r="AG8">
+        <v>2</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ8">
+        <v>30000</v>
+      </c>
+      <c r="AK8">
+        <v>32700</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="BP8">
+        <v>1</v>
+      </c>
+      <c r="BS8">
+        <v>1</v>
+      </c>
+      <c r="BT8">
+        <v>1</v>
+      </c>
+      <c r="BU8">
+        <v>1</v>
+      </c>
+      <c r="BV8">
+        <v>1</v>
+      </c>
+      <c r="BW8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:86" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="1">
+        <v>19090037</v>
+      </c>
+      <c r="C9" s="2">
+        <v>36861</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
+      </c>
+      <c r="Q9">
+        <v>5</v>
+      </c>
+      <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <v>5</v>
+      </c>
+      <c r="T9">
+        <v>5</v>
+      </c>
+      <c r="U9">
+        <v>5</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>5</v>
+      </c>
+      <c r="X9">
+        <v>5</v>
+      </c>
+      <c r="Y9">
+        <v>5</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>3</v>
+      </c>
+      <c r="AG9">
+        <v>2</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ9">
+        <v>30000</v>
+      </c>
+      <c r="AK9">
+        <v>32700</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>133</v>
+      </c>
+      <c r="AN9">
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="BB9">
+        <v>2</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BP9">
+        <v>1</v>
+      </c>
+      <c r="BS9">
+        <v>1</v>
+      </c>
+      <c r="BT9">
+        <v>1</v>
+      </c>
+      <c r="BU9">
+        <v>1</v>
+      </c>
+      <c r="BV9">
+        <v>1</v>
+      </c>
+      <c r="BW9">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A4:A5">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:A9">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/template/template_tracer.xlsx
+++ b/public/template/template_tracer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\tracer-system\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA78929C-D27F-42C2-83DC-3C42DD0618A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F0736F-73FB-4567-A075-31DA808FE0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="139">
   <si>
     <t>Nama Lengkap</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>Dukuhturi</t>
+  </si>
+  <si>
+    <t>Menurut anda seberapa besar penekanan pada metode pembelajaran dibawah ini dilaksanakan di program studi anda. - Diskusi</t>
   </si>
 </sst>
 </file>
@@ -839,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CH9"/>
+  <dimension ref="A1:CI9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -872,63 +875,64 @@
     <col min="29" max="29" width="141.42578125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="145" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="151" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="53" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="107.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="143.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="62.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="56.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="83.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="53" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="146.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="69.5703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="93.140625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="20" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="88.42578125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="109.5703125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="77.7109375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="92" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="73" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="74.28515625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="97.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="135.5703125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="100.140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="97.85546875" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="117.85546875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="86" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="115.5703125" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="159.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="84.85546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="73" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="228.85546875" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="187.5703125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="194.5703125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="237.140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="250" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="207.5703125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="187.5703125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="172.140625" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="251.28515625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="201.7109375" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="210" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="250" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="151" customWidth="1"/>
+    <col min="33" max="33" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="53" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="107.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="143.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="62.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="83.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="53" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="146.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="69.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="93.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="20" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="88.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="109.5703125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="77.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="92" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="73" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="74.28515625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="97.85546875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="135.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="97.85546875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="117.85546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="86" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="115.5703125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="159.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="84.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="96.7109375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="73" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="228.85546875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="187.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="194.5703125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="237.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="250" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="207.5703125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="187.5703125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="172.140625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="251.28515625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="201.7109375" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="210" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="250" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1023,172 +1027,175 @@
         <v>30</v>
       </c>
       <c r="AF1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -1283,9 +1290,11 @@
         <v>1</v>
       </c>
       <c r="AF2" s="1">
-        <v>5</v>
-      </c>
-      <c r="AG2" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>5</v>
+      </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -1317,31 +1326,31 @@
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
-      <c r="BM2" s="1">
-        <v>1</v>
-      </c>
-      <c r="BN2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1">
+        <v>1</v>
+      </c>
       <c r="BO2" s="1"/>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1"/>
       <c r="BR2" s="1"/>
-      <c r="BS2" s="1">
-        <v>5</v>
-      </c>
+      <c r="BS2" s="1"/>
       <c r="BT2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU2" s="1">
+        <v>4</v>
+      </c>
+      <c r="BV2" s="1">
         <v>3</v>
       </c>
-      <c r="BV2" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW2" s="1"/>
-      <c r="BX2" s="1">
-        <v>1</v>
-      </c>
-      <c r="BY2" s="1"/>
+      <c r="BW2" s="1">
+        <v>4</v>
+      </c>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1">
+        <v>1</v>
+      </c>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1"/>
       <c r="CB2" s="1"/>
@@ -1351,8 +1360,9 @@
       <c r="CF2" s="1"/>
       <c r="CG2" s="1"/>
       <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
     </row>
-    <row r="3" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>95</v>
       </c>
@@ -1449,7 +1459,9 @@
       <c r="AF3" s="1">
         <v>2</v>
       </c>
-      <c r="AG3" s="1"/>
+      <c r="AG3" s="1">
+        <v>2</v>
+      </c>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
@@ -1469,20 +1481,20 @@
       <c r="AX3" s="1"/>
       <c r="AY3" s="1"/>
       <c r="AZ3" s="1"/>
-      <c r="BA3" s="1" t="s">
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="BB3" s="1">
+      <c r="BC3" s="1">
         <v>3</v>
       </c>
-      <c r="BC3" s="1"/>
       <c r="BD3" s="1"/>
       <c r="BE3" s="1"/>
       <c r="BF3" s="1"/>
-      <c r="BG3" s="1">
-        <v>1</v>
-      </c>
-      <c r="BH3" s="1"/>
+      <c r="BG3" s="1"/>
+      <c r="BH3" s="1">
+        <v>1</v>
+      </c>
       <c r="BI3" s="1"/>
       <c r="BJ3" s="1"/>
       <c r="BK3" s="1"/>
@@ -1493,9 +1505,7 @@
       <c r="BP3" s="1"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="1"/>
-      <c r="BS3" s="1">
-        <v>1</v>
-      </c>
+      <c r="BS3" s="1"/>
       <c r="BT3" s="1">
         <v>1</v>
       </c>
@@ -1503,12 +1513,14 @@
         <v>1</v>
       </c>
       <c r="BV3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BW3" s="1">
-        <v>1</v>
-      </c>
-      <c r="BX3" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="BX3" s="1">
+        <v>1</v>
+      </c>
       <c r="BY3" s="1"/>
       <c r="BZ3" s="1"/>
       <c r="CA3" s="1"/>
@@ -1519,8 +1531,9 @@
       <c r="CF3" s="1"/>
       <c r="CG3" s="1"/>
       <c r="CH3" s="1"/>
+      <c r="CI3" s="1"/>
     </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>100</v>
       </c>
@@ -1615,30 +1628,30 @@
         <v>1</v>
       </c>
       <c r="AF4">
-        <v>4</v>
-      </c>
-      <c r="AV4">
-        <v>2</v>
-      </c>
-      <c r="AW4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>4</v>
+      </c>
+      <c r="AW4">
+        <v>2</v>
+      </c>
+      <c r="AX4" t="s">
         <v>104</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>105</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>106</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>107</v>
       </c>
-      <c r="BB4">
+      <c r="BC4">
         <v>3</v>
       </c>
-      <c r="BO4">
-        <v>1</v>
-      </c>
-      <c r="BS4">
+      <c r="BP4">
         <v>1</v>
       </c>
       <c r="BT4">
@@ -1653,8 +1666,11 @@
       <c r="BW4">
         <v>1</v>
       </c>
+      <c r="BX4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>108</v>
       </c>
@@ -1749,30 +1765,30 @@
         <v>1</v>
       </c>
       <c r="AF5">
-        <v>4</v>
-      </c>
-      <c r="AV5">
-        <v>2</v>
-      </c>
-      <c r="AW5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>4</v>
+      </c>
+      <c r="AW5">
+        <v>2</v>
+      </c>
+      <c r="AX5" t="s">
         <v>104</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>105</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>106</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>107</v>
       </c>
-      <c r="BB5">
+      <c r="BC5">
         <v>3</v>
       </c>
-      <c r="BO5">
-        <v>1</v>
-      </c>
-      <c r="BS5">
+      <c r="BP5">
         <v>1</v>
       </c>
       <c r="BT5">
@@ -1787,8 +1803,11 @@
       <c r="BW5">
         <v>1</v>
       </c>
+      <c r="BX5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
@@ -1889,52 +1908,52 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>4</v>
-      </c>
-      <c r="AI6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>115</v>
       </c>
-      <c r="AK6">
+      <c r="AL6">
         <v>36500</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AM6" t="s">
         <v>116</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AN6" t="s">
         <v>117</v>
       </c>
-      <c r="AN6">
-        <v>2</v>
-      </c>
       <c r="AO6">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>118</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>119</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>120</v>
       </c>
-      <c r="AS6">
+      <c r="AT6">
         <v>3</v>
       </c>
-      <c r="AT6">
-        <v>2</v>
-      </c>
-      <c r="BB6">
-        <v>1</v>
-      </c>
-      <c r="BD6">
-        <v>1</v>
-      </c>
-      <c r="BS6">
-        <v>2</v>
+      <c r="AU6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>1</v>
+      </c>
+      <c r="BE6">
+        <v>1</v>
       </c>
       <c r="BT6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU6">
         <v>1</v>
@@ -1942,8 +1961,11 @@
       <c r="BV6">
         <v>1</v>
       </c>
+      <c r="BW6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>121</v>
       </c>
@@ -2044,54 +2066,54 @@
         <v>1</v>
       </c>
       <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
         <v>3</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AJ7" t="s">
         <v>123</v>
       </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>40000</v>
       </c>
-      <c r="AK7">
+      <c r="AL7">
         <v>46000</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AM7" t="s">
         <v>124</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AN7" t="s">
         <v>125</v>
       </c>
-      <c r="AN7">
-        <v>2</v>
-      </c>
       <c r="AO7">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>126</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>127</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>128</v>
       </c>
-      <c r="AS7">
-        <v>2</v>
-      </c>
       <c r="AT7">
         <v>2</v>
       </c>
-      <c r="BB7">
-        <v>2</v>
-      </c>
-      <c r="BD7">
+      <c r="AU7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>2</v>
+      </c>
+      <c r="BE7">
         <v>3</v>
       </c>
-      <c r="BH7">
-        <v>1</v>
-      </c>
-      <c r="BS7">
+      <c r="BI7">
         <v>1</v>
       </c>
       <c r="BT7">
@@ -2106,8 +2128,11 @@
       <c r="BW7">
         <v>1</v>
       </c>
+      <c r="BX7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>129</v>
       </c>
@@ -2202,45 +2227,45 @@
         <v>1</v>
       </c>
       <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
         <v>3</v>
       </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
       <c r="AH8">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>131</v>
       </c>
-      <c r="AJ8">
+      <c r="AK8">
         <v>30000</v>
       </c>
-      <c r="AK8">
+      <c r="AL8">
         <v>32700</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AM8" t="s">
         <v>132</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AN8" t="s">
         <v>133</v>
       </c>
-      <c r="AN8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-      <c r="BB8">
-        <v>2</v>
-      </c>
-      <c r="BD8">
-        <v>1</v>
-      </c>
-      <c r="BP8">
-        <v>1</v>
-      </c>
-      <c r="BS8">
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="BC8">
+        <v>2</v>
+      </c>
+      <c r="BE8">
+        <v>1</v>
+      </c>
+      <c r="BQ8">
         <v>1</v>
       </c>
       <c r="BT8">
@@ -2255,8 +2280,11 @@
       <c r="BW8">
         <v>1</v>
       </c>
+      <c r="BX8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>134</v>
       </c>
@@ -2351,45 +2379,45 @@
         <v>1</v>
       </c>
       <c r="AF9">
+        <v>2</v>
+      </c>
+      <c r="AG9">
         <v>3</v>
       </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
       <c r="AH9">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>131</v>
       </c>
-      <c r="AJ9">
+      <c r="AK9">
         <v>30000</v>
       </c>
-      <c r="AK9">
+      <c r="AL9">
         <v>32700</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AM9" t="s">
         <v>132</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AN9" t="s">
         <v>133</v>
       </c>
-      <c r="AN9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>1</v>
-      </c>
-      <c r="BB9">
-        <v>2</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="BP9">
-        <v>1</v>
-      </c>
-      <c r="BS9">
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <v>1</v>
+      </c>
+      <c r="BC9">
+        <v>2</v>
+      </c>
+      <c r="BE9">
+        <v>1</v>
+      </c>
+      <c r="BQ9">
         <v>1</v>
       </c>
       <c r="BT9">
@@ -2402,6 +2430,9 @@
         <v>1</v>
       </c>
       <c r="BW9">
+        <v>1</v>
+      </c>
+      <c r="BX9">
         <v>1</v>
       </c>
     </row>

--- a/public/template/template_tracer.xlsx
+++ b/public/template/template_tracer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\tracer-system\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F0736F-73FB-4567-A075-31DA808FE0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA60AAE6-DB44-461F-AD51-6DBA92C66460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,9 +169,6 @@
     <t>Nama Perguruan Tinggi</t>
   </si>
   <si>
-    <t>Program studi</t>
-  </si>
-  <si>
     <t>Tanggal masuk</t>
   </si>
   <si>
@@ -437,6 +434,9 @@
   </si>
   <si>
     <t>Menurut anda seberapa besar penekanan pada metode pembelajaran dibawah ini dilaksanakan di program studi anda. - Diskusi</t>
+  </si>
+  <si>
+    <t>Program Studi Lanjut</t>
   </si>
 </sst>
 </file>
@@ -483,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -497,6 +497,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,7 +1028,7 @@
         <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG1" t="s">
         <v>31</v>
@@ -1083,121 +1084,121 @@
       <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AZ1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>84</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1">
         <v>17090093</v>
@@ -1206,25 +1207,25 @@
         <v>36861</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F2" s="1">
         <v>2023</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K2" s="1">
         <v>4</v>
@@ -1364,7 +1365,7 @@
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1">
         <v>18090072</v>
@@ -1373,25 +1374,25 @@
         <v>36861</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F3" s="1">
         <v>2023</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K3" s="1">
         <v>3</v>
@@ -1483,7 +1484,7 @@
       <c r="AZ3" s="1"/>
       <c r="BA3" s="1"/>
       <c r="BB3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BC3" s="1">
         <v>3</v>
@@ -1535,7 +1536,7 @@
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="1">
         <v>19090039</v>
@@ -1544,109 +1545,109 @@
         <v>36861</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F4" s="1">
         <v>2023</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4">
+        <v>4</v>
+      </c>
+      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="R4">
+        <v>4</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>5</v>
+      </c>
+      <c r="U4">
+        <v>5</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>5</v>
+      </c>
+      <c r="X4">
+        <v>5</v>
+      </c>
+      <c r="Y4">
+        <v>5</v>
+      </c>
+      <c r="Z4">
+        <v>2</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>2</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>2</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>4</v>
+      </c>
+      <c r="AW4">
+        <v>2</v>
+      </c>
+      <c r="AX4" t="s">
         <v>103</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
-      </c>
-      <c r="N4">
-        <v>4</v>
-      </c>
-      <c r="O4">
-        <v>4</v>
-      </c>
-      <c r="P4">
-        <v>4</v>
-      </c>
-      <c r="Q4">
-        <v>4</v>
-      </c>
-      <c r="R4">
-        <v>4</v>
-      </c>
-      <c r="S4">
-        <v>5</v>
-      </c>
-      <c r="T4">
-        <v>5</v>
-      </c>
-      <c r="U4">
-        <v>5</v>
-      </c>
-      <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="W4">
-        <v>5</v>
-      </c>
-      <c r="X4">
-        <v>5</v>
-      </c>
-      <c r="Y4">
-        <v>5</v>
-      </c>
-      <c r="Z4">
-        <v>2</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>2</v>
-      </c>
-      <c r="AC4">
-        <v>1</v>
-      </c>
-      <c r="AD4">
-        <v>2</v>
-      </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-      <c r="AF4">
-        <v>1</v>
-      </c>
-      <c r="AG4">
-        <v>4</v>
-      </c>
-      <c r="AW4">
-        <v>2</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>104</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>105</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>106</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>107</v>
       </c>
       <c r="BC4">
         <v>3</v>
@@ -1672,7 +1673,7 @@
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1">
         <v>19090043</v>
@@ -1681,26 +1682,26 @@
         <v>36861</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F5" s="1">
         <v>2023</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="K5">
         <v>5</v>
       </c>
@@ -1774,16 +1775,16 @@
         <v>2</v>
       </c>
       <c r="AX5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY5" t="s">
         <v>104</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>105</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>106</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>107</v>
       </c>
       <c r="BC5">
         <v>3</v>
@@ -1809,7 +1810,7 @@
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="1">
         <v>18090108</v>
@@ -1818,127 +1819,127 @@
         <v>36861</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F6" s="1">
         <v>2023</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>2</v>
+      </c>
+      <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AA6">
+        <v>2</v>
+      </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>114</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-      <c r="N6">
-        <v>2</v>
-      </c>
-      <c r="O6">
-        <v>2</v>
-      </c>
-      <c r="P6">
-        <v>2</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-      <c r="R6">
-        <v>2</v>
-      </c>
-      <c r="S6">
-        <v>2</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
-      </c>
-      <c r="U6">
-        <v>2</v>
-      </c>
-      <c r="V6">
-        <v>2</v>
-      </c>
-      <c r="W6">
-        <v>2</v>
-      </c>
-      <c r="X6">
-        <v>2</v>
-      </c>
-      <c r="Y6">
-        <v>2</v>
-      </c>
-      <c r="Z6">
-        <v>2</v>
-      </c>
-      <c r="AA6">
-        <v>2</v>
-      </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
-      <c r="AC6">
-        <v>2</v>
-      </c>
-      <c r="AD6">
-        <v>2</v>
-      </c>
-      <c r="AE6">
-        <v>2</v>
-      </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
-      <c r="AG6">
-        <v>1</v>
-      </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6">
-        <v>4</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>115</v>
       </c>
       <c r="AL6">
         <v>36500</v>
       </c>
       <c r="AM6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AN6" t="s">
         <v>116</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6">
+        <v>2</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>117</v>
       </c>
-      <c r="AO6">
-        <v>2</v>
-      </c>
-      <c r="AP6">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>118</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>119</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>120</v>
       </c>
       <c r="AT6">
         <v>3</v>
@@ -1967,7 +1968,7 @@
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="1">
         <v>18090123</v>
@@ -1976,25 +1977,25 @@
         <v>36861</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F7" s="1">
         <v>2023</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -2072,7 +2073,7 @@
         <v>3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK7">
         <v>40000</v>
@@ -2081,25 +2082,25 @@
         <v>46000</v>
       </c>
       <c r="AM7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN7" t="s">
         <v>124</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7">
+        <v>2</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>125</v>
       </c>
-      <c r="AO7">
-        <v>2</v>
-      </c>
-      <c r="AP7">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>126</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>127</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>128</v>
       </c>
       <c r="AT7">
         <v>2</v>
@@ -2134,7 +2135,7 @@
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" s="1">
         <v>19090022</v>
@@ -2143,25 +2144,25 @@
         <v>36861</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F8" s="1">
         <v>2023</v>
       </c>
       <c r="G8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" t="s">
         <v>102</v>
       </c>
-      <c r="I8" t="s">
-        <v>103</v>
-      </c>
       <c r="J8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -2239,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK8">
         <v>30000</v>
@@ -2248,10 +2249,10 @@
         <v>32700</v>
       </c>
       <c r="AM8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AN8" t="s">
         <v>132</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>133</v>
       </c>
       <c r="AO8">
         <v>1</v>
@@ -2286,7 +2287,7 @@
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="1">
         <v>19090037</v>
@@ -2295,25 +2296,25 @@
         <v>36861</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F9" s="1">
         <v>2023</v>
       </c>
       <c r="G9" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" t="s">
         <v>135</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>136</v>
       </c>
-      <c r="I9" t="s">
-        <v>137</v>
-      </c>
       <c r="J9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2391,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK9">
         <v>30000</v>
@@ -2400,10 +2401,10 @@
         <v>32700</v>
       </c>
       <c r="AM9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AN9" t="s">
         <v>132</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>133</v>
       </c>
       <c r="AO9">
         <v>1</v>
